--- a/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
+++ b/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
@@ -466,6 +466,36 @@
           <t>陳富 CHEN Fu</t>
         </is>
       </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>邊境少女 / Border Girls（提案名，未查到任何完成、放映或發行紀錄）</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>以「陳富 CHEN Fu」及片名「邊境少女／Border Girls」多次搜尋，僅查到同名導演陳國富（Chen Kuo-fu，商業片導演）等不相關結果，找不到與此提案相符的紀錄片完成紀錄、CNEX/CCDF 作品頁或影展資料。無法確認此片是否完成，亦無法確認提案人陳富的身分（可能為較不知名之獨立製片者）。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -487,6 +517,39 @@
           <t>Risa MORIMOTO / 李嘉雯 Diana Chiawen LEE</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>未能確認唯一定案片名。導演 Risa Morimoto 名下有兩部主題相近的紀錄片：《Code Red: China's Internet Revolution》（ITVS 出品，探討中國網路審查）與《Broken Harmony: China's Dissidents》（2019，探討中國異議人士／網路審查受害者）。提案名「Code Red」與前者字面相同，但無法確認何者即為此次 CCDF-1 提案之最終成片，也可能兩者皆與此提案有淵源（主題延續、多年後才完成）。</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>https://itvs.org/films/code-red/
+https://www.imdb.com/title/tt9657798/
+https://www.firelightmedia.tv/filmmakers/risa-morimoto
+https://sites.google.com/site/dianacleecv/</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>提案人為 Risa Morimoto 與李嘉雯 Diana Chiawen Lee。查到 Risa Morimoto 確實長期關注中國網路審查／異議人士題材，名下有《Code Red: China's Internet Revolution》及《Broken Harmony: China's Dissidents》(2019) 兩部紀錄片，但因 itvs.org、firelightmedia.tv、dianachiawenlee.com 等關鍵頁面在此環境下被 egress proxy 擋下，無法直接讀取內容核實兩者與此提案的關係、確切完成年份或聯絡方式。李嘉雯 Diana Chiawen Lee 後續較知名的作品為《日常對話 Small Talk》製片，未查到她在 Code Red 中的具體角色資料。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -513,6 +576,36 @@
           <t>史祖德 Gary SHIH / 霍寧 HUO Ning</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>掘土人 / The Tomb Digger（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>http://www.cnex.org.tw/productions_other.php?sign=cnexstudiotw</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>已於 CNEX 監製作品目錄中查到本片，內容描述 2008 年冬天河南安陽考古隊搶救東漢古墓，考古隊長潘偉斌認為此墓即為曹操墓，2010 年該墓入選中國十大考古發現之一並引發學界爭議，導演正是史祖德、霍寧，與提案資訊吻合，可確認為已完成之 CNEX 監製作品。因 tw.cnexdoc.com、cnex.org.tw 等頁面在此環境下被 egress proxy 擋下，無法進一步取得聯絡email。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -539,6 +632,36 @@
           <t>李軍虎 LI Jun-hu</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>新片名：換城 / Where Should I Go?（提案名：洗腳 / Where I Should Go）</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>https://tw.cnexdoc.com/zh/productions/1163/</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>CNEX 基金會官網「換城 Where Should I Go?」作品頁確認導演為李軍虎，2010年出品，70分鐘，中國作品，內容講述農村移居城市家庭的抉擇（母親張志莉留下兩名年幼女兒在鄉下、帶兒子進城讀書；楊秀清用亡夫撫恤金為子女買城市戶口等故事），與提案人李軍虎相符，可判斷中文片名由《洗腳》改為《換城》，英文片名維持相近（Where I Should Go → Where Should I Go?）。因 tw.cnexdoc.com 頁面被 egress proxy 擋下無法直接讀取全文，聯絡email未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -565,6 +688,36 @@
           <t>蔡崇隆 TSAI Tsung-lung / 蕭立峻 Richard HSIAO</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>機器○人 / Man-chine（提案名，未查到完成紀錄）</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.tfai.org.tw/zh-hant/filmmakers/1933</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>蔡崇隆為知名紀錄片導演，代表作包括《島國殺人紀事》、《失婚記》、《再見 可愛陌生人》、《九槍》（2022金馬最佳紀錄片）等，蕭立峻則為《九槍》攝影師之一，兩人確實有長期合作關係，但在 TaiwanDocs 台灣紀錄片資料庫及多次搜尋中，均查無《機器○人》或《Man-chine》這部作品，也未見蔡崇隆的移工機器人相關主題紀錄片。研判此案可能未完成、已改名為其他作品，或规模較小未被資料庫收錄，無法確認。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -591,6 +744,36 @@
           <t>章大中 CHANG Ta-chung</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>找不到國小 / School From No Where（提案名，未查到完成紀錄）</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>多次搜尋「章大中」導演及片名「找不到國小」，僅查到同名兒童讀物（岑澎維著），與紀錄片提案人「章大中 CHANG Ta-chung」及《找不到國小》紀錄片本身完全無關聯資料，查無此人任何紀錄片作品紀錄、CNEX/CCDF 頁面或影展資料，無法確認此案是否完成或提案人身分。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -617,6 +800,38 @@
           <t>葉雲 YE Yun</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>對看 / Look Love（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>http://app2.atmovies.com.tw/film/ffcn21677819/
+https://www.thenewslens.com/feature/2016cnex/48492
+https://movie.douban.com/subject/26638107/</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>確認為葉雲執導之紀錄片，2015年完成，獲釜山國際影展最佳紀錄片，並入選山形國際紀錄片影展亞洲新浪潮單元、阿姆斯特丹國際紀錄片影展（IDFA）新人競賽單元，片長146分鐘，內容為北京私立小學與湘西深山小學兩地孩童對照。片名與提案名完全相同，導演姓名亦相符，確認度高。未查到公開聯絡email。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -669,6 +884,38 @@
           <t>陳惠美 Vivien H.M. CHEN / 莊濟寰 Roger C.H. CHUANG</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>墨魂 / Inky Soul（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://archive.ncafroc.org.tw/result?id=73607d951f974900b9e0babe1b7bbd0a
+https://ccdf.cnexdoc.com/en/ccdf-awarded/4667/
+https://www.imdb.com/title/tt13660992/</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>國藝會補助成果檔案庫、CCDF官網得獎頁與IMDb均收錄本片，導演陳惠美、監製莊濟寰，攝影溫瑞鳴，2012年作品，內容講述台灣兩位當代刺青藝術家追溯泰雅族傳統紋面文化、重建台灣刺青史的故事，片長約75分鐘。提案人陳惠美、莊濟寰與導演、監製姓名完全吻合，確認度高。因相關頁面於此環境下被 egress proxy 擋下無法讀取全文，聯絡email未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -695,6 +942,38 @@
           <t>李靖惠 Jasmine C.H. LEE</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>麵包情人 / Money and Honey（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://taiwancinema.bamid.gov.tw/Staff/StaffContent/?ContentUrl=35420
+https://docs.tfai.org.tw/zh-hant/film/4286
+http://www.epochtimes.com/b5/12/9/17/n3684663.htm</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>確認為李靖惠執導之「家國系列紀錄片」第六部作品，耗時13年拍攝台北養老院菲籍看護工「菲媽」的故事，2012年完成並入圍金馬獎最佳紀錄片、最佳剪輯，另獲十餘項國際影展獎項，並入選文化部「台灣電影工具箱」十大代表作之一。片名與提案人皆與資料相符，確認度高。因 taiwancinema.bamid.gov.tw、docs.tfai.org.tw 頁面在此環境下被 egress proxy 擋下無法讀取全文，聯絡email未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -719,6 +998,38 @@
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>黃茂昌 Patrick HUANG</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>是（但需注意可能非同一組主創）</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>海上情書（中文片名與提案名相同；英文片名未能於公開資料中確認，提案英文名為 Trapped at Sea, Lost in Time，未見於後續公開資料中）</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://taiwancinema.bamid.gov.tw/Film/FilmContent/?ContentUrl=73056
+https://www.marieclaire.com.tw/entertainment/movie/19723
+https://docs.tfai.org.tw/zh-hant/filmmakers/2445</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>查到一部同名紀錄片《海上情書》，耗時六年拍攝、為台灣首部關注遠洋漁業的紀錄片，由《跳舞時代》金馬最佳紀錄片導演郭珍弟與新導演柯能源共同執導，記錄一艘高雄前鎮出港的遠洋鮪魚圍網船三年漁撈歷程，曾在前鎮漁港舉辦全台首次「船上首映會」。提案人黃茂昌（Patrick Mao Huang，知名紀錄片製片／前景娛樂負責人）姓名並未出現在導演欄，研判其角色應為監製／製片而非導演，與提案資料中僅列黃茂昌一人略有出入，但中文片名完全相同、題材（海上生活、對家的思念）亦高度吻合，推測應為同一提案發展而成的作品，惟導演組合的對應關係無法百分之百確認。因 taiwancinema.bamid.gov.tw、docs.tfai.org.tw 頁面被 egress proxy 擋下無法讀取全文細節，聯絡email未查到。</t>
         </is>
       </c>
     </row>
@@ -1864,6 +2175,36 @@
           <t>梁邁 LIANG Mai / （原提案片名：多少次散場，忘了憂傷）                                                             戴年文 DAI Nian-wen</t>
         </is>
       </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>未查到確切完成作品（提案名：非常舞蹈 / Twist；原提案片名：多少次散場，忘了憂傷）</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>以「梁邁」「戴年文」及片名「非常舞蹈」「Twist」多方查詢，皆未找到對應的紀錄片完成紀錄、影展資料或發行資訊，無法確認是否完成。查詢預算已用盡，建議之後補查 CNEX CCDF-4（2013）官方歷屆名單頁面。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1890,6 +2231,39 @@
           <t>Nicola CONTINI / Alessandro CARROLI</t>
         </is>
       </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Il segreto delle calze（英文發行片名：Hold Me Tight(s)）/ 絲襪的秘密（提案名：絲襪的秘密 / The Secret Behind the Stockings，義大利文原片名與提案英文名不同，中文名相同）</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>stefano.mutolo@gmail.com</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>發行代理 Berta Film（聯絡人 Stefano Mutolo）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mymovies.it/film/2015/ilsegretodellecalze/
+https://ep.ji-hlava.com/producers/alessandro-carroli
+https://www.eiefilm.com/en/project/il-segreto-delle-calze/
+http://www.bertafilm.com/catalogue/il-segreto-delle-calze/</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>以導演 Nicola CONTINI 及主題（絲襪／製襪業）比對，確認即為義大利紀錄片《Il segreto delle calze》（英文片名 Hold Me Tight(s)），2015 年完成，片長 60 分鐘，由 EiE Film、Kin Società Cooperativa 製作，ARTE 合製。Alessandro CARROLI 為該片相關製片人（Emerging Producers／Ji.hlava 資料庫列名）。發行聯絡 email 見於 Berta Film 片單頁面搜尋結果。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1916,6 +2290,40 @@
           <t>羅恩惠 Connie Y.W. LO / 葉漢明 IP Hon-ming</t>
         </is>
       </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>消失的檔案 / Vanished Archives（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/zh-hant/%E6%B6%88%E5%A4%B1%E7%9A%84%E6%AA%94%E6%A1%88
+https://en.wikipedia.org/wiki/Vanished_Archives
+https://vanishedarchives.org/
+https://www.facebook.com/vanishedarchives/?locale=zh_HK
+https://zh.wikipedia.org/zh-tw/%E7%BE%85%E6%81%A9%E6%83%A0</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>導演羅恩惠（Connie Y.W. LO）與片名皆吻合，該片 2017 年於香港首映，內容為 1967 年香港暴動相關檔案調查，歷時 4 年拍攝完成，並曾於美加多地放映。官方網站 vanishedarchives.org 及 Facebook 專頁因網路存取限制（egress proxy 封鎖）無法直接讀取頁面內容確認 email，故列為未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1942,6 +2350,36 @@
           <t>康世偉 Ben KANG / 王鑫 WANG Xin</t>
         </is>
       </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>詩之一生 / A Lifetime Poem（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt4339104/</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>IMDb 收錄有同名紀錄片《A Lifetime Poem》（2015 年前後），內容描述詩人「康世偉」的生命故事，與提案人「康世偉 Ben KANG」姓名完全吻合，推測為以自身生命故事為題材的紀錄片（康世偉可能身兼導演與主角）。因 IMDb 頁面遭網路存取限制無法直接讀取完整工作人員名單，無法百分之百確認「王鑫 WANG Xin」的角色（製片／導演），故完成度判斷為「是」但比對細節仍有不確定之處。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1962,6 +2400,39 @@
           <t>侯祖辛 HOU Zu-xin / 劉斌 LIU Bin</t>
         </is>
       </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>未確認（提案名：40 60；查得侯祖辛另有以其父親搖滾生涯為題材之作品《老摇滚》/《ROCK ON, 20.40.60》，年齡「20、40、60」與提案名「40 60」高度相關，但無法確認是否為同一部片的最終版本）</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bilibili.com/video/BV177411U79a/
+https://www.zhihu.com/question/40920100
+https://www.xinpianchang.com/a10402209
+https://movie.douban.com/celebrity/1441426/</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>侯祖辛（HOU Zu-xin）另有紀錄片作品《老摇滚》（英文或作 ROCK ON, 20.40.60），描述其父親侯牧人（中國第一代搖滾樂手）於 20、40、60 歲的搖滾生涯，曾獲華沙影展最佳短紀錄片等獎項。此作品的年齡意象與 CCDF 提案名「40 60」相符，很可能是同一計畫的最終或階段性成果，但查無明確資料證實兩者為同一項目，亦查無提案共同提報人「劉斌 LIU Bin」的相關資訊，故完成度保守列為「未查到」。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2008,6 +2479,36 @@
           <t>Female Pachiachiang</t>
         </is>
       </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>未確認（提案名：女神降臨 / Female Pachiachiang；查得同名主題紀錄片描述花蓮光復鄉女子八家將團隊，年代與內容相符，但無法確認導演身分及片名是否完全一致，proposer 欄位原始資料缺失）</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/zh-tw/%E5%B0%91%E5%A5%B3%E5%85%AB%E5%AE%B6%E5%B0%87</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>由於本筆資料 proposer 欄位為 null，無法用導演姓名交叉比對。搜尋結果指出確有一部 2014 年台灣紀錄片，描述花蓮光復鄉北園宮女子八家將團隊（2008 年獲全國八家將比賽第二名），主題與提案片名「女神降臨 / Female Pachiachiang」高度吻合，但無法取得明確可信來源確認正式片名、導演與完成狀態，故列為未查到，僅供後續查證參考。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2028,6 +2529,40 @@
           <t>From Now On</t>
         </is>
       </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>此後 / From Now On（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>luminosofilm@gmail.com</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>導演陳文彬（光之路電影 Luminoso Film）</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>http://classic-blog.udn.com/webman/130158262
+https://www.tidf.org.tw/zh-hant/films/63830
+https://www.tidf.org.tw/zh-hant/reportsandarticle/64743
+http://luminosofilm.tw/電影作品/
+https://www.facebook.com/AkiraChenFans/</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>2016 年完成，導演陳文彬耗時七年記錄 2009 年莫拉克風災小林村居民翁瑞琪的故事，片名與提案名完全相同。email 為陳文彬所屬光之路電影（Luminoso Film）公開聯絡信箱，多筆搜尋結果將此信箱與陳文彬本人連結。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2048,6 +2583,41 @@
           <t>TPE-TICs</t>
         </is>
       </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>台北抽搐 / TPE-Tics（提案名寫作 TPE-TICs，大小寫略有差異，其餘相同）</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>jadejessica@gmail.com</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>導演林婉玉本人</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://movie.douban.com/subject/26345146/
+https://www.imdb.com/title/tt4805922/
+https://www.thenewslens.com/article/31421
+https://docs.tfai.org.tw/zh-hant/filmmakers/1953
+https://www.facebook.com/jadejessica
+http://jadejessica.weebly.com/tpe-tics.html</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>2015 年完成，導演林婉玉（proposer 欄位雖為 null，但片名唯一且明確對應），描述聲音藝術家黃大旺，於台北電影節首映並獲評審團特別獎。email 見於林婉玉個人網站 jadejessica.weebly.com 及同名 Facebook 帳號（因網路存取限制未能直接開啟頁面逐字核對，但多筆獨立搜尋結果一致指向此信箱與其本人）。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2068,6 +2638,39 @@
           <t>Jade Miners / 項目    （Original title: The Jade）</t>
         </is>
       </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>挖玉石的人 / Jade Miners（與提案名相同；提案註記原片名 The Jade 應為早期暫定英文名，最終定名 Jade Miners）</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/zh/%E6%8C%96%E7%8E%89%E7%9F%B3%E7%9A%84%E4%BA%BA
+https://www.tidf.org.tw/zh-hant/films/20549
+https://viewpoint.pts.org.tw/video/500
+https://taiwancinema.bamid.gov.tw/EngCompany/EngCompanyContent/?ContentUrl=65804</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>2015 年台北電影節首映，導演趙德胤（Midi Z）首部紀錄長片，記錄緬甸克欽邦戰區玉礦工人，2016 年獲 TIDF 台灣競賽優等獎。片名與提案完全吻合（proposer 欄位為 null，以片名唯一性判定）。製作公司 Seashore Image Productions 之台灣電影網頁面因網路存取限制無法讀取，未能取得公開 email。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2092,6 +2695,38 @@
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>龔萬祥 Sean, W.H.KUNG</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>回家吃自己 / No Country for Young Man（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://archive.ncafroc.org.tw/result?id=71db16b0f2bc48f59f5f7b26dc1dca07
+https://www.youtube.com/watch?v=QC15gG555oc
+http://spot-link.com/film?id=205</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>導演龔萬祥（Sean W.H. KUNG）與片名完全吻合，記錄青年楊宇帆返鄉從事有機鳳梨農業、與祖孫三代情感的故事，獲國藝會補助並於 2014 年獲新北市紀錄片獎優選。查無公開可靠 email。</t>
         </is>
       </c>
     </row>
@@ -2752,6 +3387,37 @@
           <t>徐瑋超 XU Wei-chao</t>
         </is>
       </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>告別十二歲 / Heart of a Lion（與提案名相同，英文片名確認；中文片名未能交叉確認）</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt11229646/
+https://www.firstfilm.org.cn/en/movies-en/film-library-en/heart-of-a-lion/</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>查得 IMDb 上有 2020 年紀錄片《Heart of a Lion》詞條，且中國 FIRST 青年影展片庫亦收錄同名作品，與提案英文片名相符，判斷應為同一計畫並已完成。惟因本次研究工具（WebSearch 配額用盡、WebFetch 遭網路出口代理封鎖）於查證過程中失效，無法進一步擷取頁面內容確認導演徐瑋超掛名、確切中文片名與是否更名，亦未查到聯絡信箱，建議後續補查。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2778,6 +3444,36 @@
           <t>孫揚 SUN Yang / （Original title: Ma Liang’s Time Machine）                              黃俊如 Wendy HUANG</t>
         </is>
       </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：時光機 / Our Time Machine）</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>本項目查證時研究工具已失效（WebSearch 當日配額用盡、WebFetch 遭網路出口代理封鎖，包含 IMDb、Wikipedia、CNEX、Google／Bing／DuckDuckGo 等站台皆無法存取），未能進行任何搜尋即中斷，故完成狀態、正式片名與聯絡信箱均未查到。備註：此片依 CLAUDE 記憶應為孫揚執導、黃俊如監製的動畫紀錄片，曾入圍多個國際影展（含翠貝卡影展），但因本次工具限制未能實際查證來源，此推測不列入正式結論，僅供後續人工查證參考。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2804,6 +3500,36 @@
           <t>王申 WANG Sean 陳延企 Chris CHEN</t>
         </is>
       </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：聯合公寓 / The United House）</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>同上，本次研究工具（WebSearch、WebFetch）於查證過程中失效，未能進行搜尋，故完成狀態、正式片名與聯絡信箱均未查到，建議後續補查。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2830,6 +3556,36 @@
           <t>馬智恆 MA Chi-hang</t>
         </is>
       </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：岸上漁歌 / Ballad on the Shore）</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>同上，本次研究工具（WebSearch、WebFetch）於查證過程中失效，未能進行搜尋，故完成狀態、正式片名與聯絡信箱均未查到，建議後續補查。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2856,6 +3612,36 @@
           <t>陳志漢 Maso CHEN</t>
         </is>
       </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：文林銀行 / Bank in School）</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>同上，本次研究工具（WebSearch、WebFetch）於查證過程中失效，未能進行搜尋，故完成狀態、正式片名與聯絡信箱均未查到。備註：依 CLAUDE 背景知識，此片導演陳志漢（Maso CHEN）另有作品《那個靜默的陽光午後》，本片後續是否完成需人工查證，此處不作為正式結論。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2882,6 +3668,36 @@
           <t>王申 Sean WANG / （原提案片名：夫子方舟 Original title: Arks of Confucius）                                趙佳 ZHAO Jia</t>
         </is>
       </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：芳舟 / Lady of the Harbour，原提案片名：夫子方舟 Arks of Confucius）</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>同上，本次研究工具（WebSearch、WebFetch）於查證過程中失效，未能進行搜尋，故完成狀態、正式片名與聯絡信箱均未查到，建議後續補查。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2906,6 +3722,36 @@
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>陳琦 CHEN Qi / （原提案片名：我的世界 Original title: Mine World, My Word）</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：我跟著你 / I Follow You，原提案片名：我的世界 Mine World, My Word）</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>同上，本次研究工具（WebSearch、WebFetch）於查證過程中失效，未能進行搜尋，故完成狀態、正式片名與聯絡信箱均未查到，建議後續補查。</t>
         </is>
       </c>
     </row>

--- a/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
+++ b/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
@@ -1058,6 +1058,38 @@
           <t>王利波 WANG Li-bo</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>三峽啊 / San Xia（提案名：Oh, The San Xia，英文片名於各資料庫拼法略有出入，中文片名與提案相同）</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://helanonline.cn/archive/article/3792
+https://zh.wikipedia.org/zh-tw/%E4%B8%AD%E5%8D%8E%E4%BA%BA%E6%B0%91%E5%85%B1%E5%92%8C%E5%9B%BD%E8%A2%AB%E7%A6%81%E7%94%B5%E5%BD%B1%E5%88%97%E8%A1%A8
+https://chinadigitaltimes.net/space/%E7%A6%81%E7%89%87%E7%9B%AE%E5%BD%95</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>王利波執導，2012 年完成，108 分鐘。因題材敏感，中國大陸另剪了電視版《三峽江湖》於香港陽光衛視播出，本片《三峽啊》為導演版，在香港國際電影節世界首映。片子被列入中國大陸禁片名單，但確實已完成並曾對外放映，故列為「是」。查無導演或製作公司公開聯絡 email，王利波為獨立紀錄片工作者，公開聯絡資訊極少見。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1084,6 +1116,39 @@
           <t>王楊 WANG Yang</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>紡織城 / Weaving（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/253925833_100048878
+https://www.jiemian.com/article/2736869.html
+https://asianmoviepulse.com/2025/09/weaving-2017-by-wang-yang-cathayplay-film-review/
+https://zh.wikipedia.org/zh-hans/%E7%8E%8B%E6%9D%A8</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>王楊執導，耗時 6 年拍攝西安紡織城拆遷紀事，2017 年完成，於多倫多國際紀錄片影展（Hot Docs）世界首映，並獲 2018 莫斯科國際紀錄片影展最佳導演獎。現由 CathayPlay 線上發行。查無導演或 CathayPlay 公開聯絡 email（CathayPlay 官網因網路存取限制無法讀取）。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1110,6 +1175,39 @@
           <t>郝智強 HAO Zhi-quiang</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>跑酷少年 / Bazaar Jumpers（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt2643320/
+https://vimeo.com/752402217
+https://catalog.libraries.psu.edu/catalog/20062077
+https://www.yesasia.com/us/bazaar-jumpers-dvd-english-subtitled-taiwan-version/1036097658-0-0-0-en/info.html</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>郝智強執導，2012 年由 CNEX 出品、北京龍馬風文化傳播製作完成，記錄兩位維吾爾族跑酷少年的故事，獲上海電視節最佳中國紀錄片獎，並已發行 DVD 及線上點播（Vimeo On Demand）。查無公開聯絡 email；IMDb、PSU 圖書館目錄等頁面因存取限制無法進一步核對。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1136,6 +1234,39 @@
           <t>黎小鋒 LI Xiao-feng</t>
         </is>
       </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>昨日狂想曲 / The Shoeshiner's Journey（提案名：The Shoe Shiner's Journey，中文片名相同，英文拼法略有差異）</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://movie.douban.com/subject/26602235/
+https://m.thepaper.cn/newsDetail_forward_1454773
+https://baike.baidu.com/item/%E6%98%A8%E6%97%A5%E7%8B%82%E6%83%B3%E6%9B%B2/19736386
+https://tw.cnexdoc.com/zh/productions/1097/</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>黎小鋒與賈愷聯合執導，歷時 8 年拍攝，2016 年 7 月於 FIRST 青年電影展首映並獲最佳紀錄片獎。CNEX 監製頁面上英文片名拼為「THE SHOESHINNER'S JOURNEY」，與提案的「The Shoe Shiner's Journey」用字略有差異，中文片名一致。查無導演公開聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1162,6 +1293,38 @@
           <t>黃建亮 Albert HUANG</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>宅．私塾 / Home School（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://taiwancinema.bamid.gov.tw/EngStaff/PrintFrameContent?ContentUrl=65640
+https://tw.cnexdoc.com/zh/productions/1111/
+https://www.photoonetaipei.com/reviewers-2020-albert-jl-huang</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>黃建亮（Albert J.L. HUANG）執導，2013 年完成，60 分鐘，探討台灣四個家庭選擇在家自學的故事，由 CNEX 監製。查無黃建亮或製作公司公開聯絡 email；台灣電影網頁面因網路存取限制無法直接讀取確認。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1188,6 +1351,37 @@
           <t>王文明 WANG Wen-ming</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>風沙線上 / Whisper of Minqin（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/240407612_100048878
+https://www.youtube.com/watch?v=0XMWu2NOZF8</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>王文明執導，記錄甘肅民勤兩戶人家對抗沙漠化侵蝕家園的故事，由 CNEX Studio 監製，已完成並釋出正式預告片，也曾在中國放映活動（如「CNEX MOVIES」）中放映。查無導演公開聯絡 email；CNEX Studio 官網（cnex.tw / cnex.com.tw）因網路存取限制無法讀取。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1214,6 +1408,39 @@
           <t>王淼 WANG Miao</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>尋岸 / Maineland（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodreporter.com/movies/movie-reviews/maineland-984695/
+https://mainelandfilm.com/
+https://www.amazon.com/Maineland-Stella-Xinyi-Zhu/dp/B071WS4PF5
+https://www.sohu.com/a/239347064_330565</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>王淼執導，2017 年完成並於 SXSW 影展首映獲評審團特別獎，後於 Amazon Prime Video 等平台上架，並在中國舉辦過映後座談。查無公開聯絡 email；官方網站 mainelandfilm.com 因網路存取限制無法讀取聯絡頁。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1235,6 +1462,38 @@
           <t>HO Chao-ti</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>我愛高跟鞋 / My Fancy High Heels（原始資料表此列 zh/en 欄位為提案人姓名「賀照緹 / HO Chao-ti」，proposer 欄位為空，研判為表格資料誤植，提案片名缺失；依提案人與屆別〔CCDF-2，約 2011 年〕比對，最相符者為賀照緹同期完成的紀錄片《我愛高跟鞋》）</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>https://news.pts.org.tw/article/160159
+https://zh.wikipedia.org/wiki/%E6%88%91%E6%84%9B%E9%AB%98%E8%B7%9F%E9%9E%8B
+https://tw.news.yahoo.com/%E6%88%91%E6%84%9B%E9%AB%98%E8%B7%9F%E9%9E%8B-%E6%8F%AD%E5%90%8D%E7%89%8C%E5%89%9D%E5%89%8A%E7%9C%9F%E7%9B%B8-160000038.html</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>此列資料明顯有誤：zh/en 欄位填的是提案人姓名而非片名，proposer 欄位反而是空的，無法百分之百確認對應片名。根據賀照緹於 CCDF-2（約 2011 年）前後的創作軌跡，最可能對應的是她 2011 年完成、耗時兩年拍攝的紀錄片《我愛高跟鞋 My Fancy High Heels》，探討名牌高跟鞋背後的血汗代工與皮革產業，2012 年獲第 55 屆紐約國際電視電影節優等獎。此為合理推測而非確證，請人工複核原始提案資料。查無賀照緹本人公開聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1261,6 +1520,36 @@
           <t>何泱 Alice HO</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：養奢 / Farming Luxuries）</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>多次以中英文關鍵字（何泱、Alice HO、養奢、Farming Luxuries）搜尋，查無任何與此提案相符的後續完成、放映或發行紀錄，亦查無提案人「何泱 Alice HO」的其他公開資訊。研判此案可能未完成、未公開發表，或提案人使用其他筆名 / 已更名之片名，需人工進一步查證（如向 CNEX/CCDF 直接查詢歷屆提案檔案）。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1287,6 +1576,38 @@
           <t>章大中 CHANG Ta-chung</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>看不見的跑道 / Forever Runner（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.merit-times.com/NewsPage.aspx?unid=299458
+https://funscreen.org/article/5905
+https://www.tidf.org.tw/zh-hant/news/5371</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>章大中執導，2013 年完成，70 分鐘，記錄台灣超級馬拉松紀錄保持人邱淑容因敗血症截肢後復健、重返賽道的故事，曾於台灣院線及影展放映。查無章大中或製作方公開聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1313,6 +1634,39 @@
           <t>盧幹文 K.M.LO</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>三輪車電影 / Tuk Tuk Cinema（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>tuktukcinema@gmail.com</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>K.M. LO（導演本人／Tuk Tuk Cinema 團隊）</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt30489820/
+https://www.indiegogo.com/en/projects/kmlo/tuk-tuk-cinema
+https://cathayplay.com/films/tuk-tuk-cinema/
+https://www.hkfringeclub.com/en/whatson/1336-Tuk+Tuk+Cinema+Summer+Workshop.html</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>IMDb 及 CathayPlay 皆列有 2022 年紀錄片《Tuk Tuk Cinema》，內容為導演 K.M. Lo（盧幹文）以三輪車移動放映車在發展中國家教學拍片與放映，主題與提案名「三輪車電影」高度吻合，惟提案為 CCDF-2（約 2011 年），距完成上映約十年，時間跨度大，建議再以官方管道複核為同一計畫。email 取自 Fringe Club 活動頁面之搜尋摘要（提及可寫信至該信箱洽詢工作坊合作），本次因網路存取限制未能直接開啟原始網頁逐字核對，信心中等。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1339,6 +1693,36 @@
           <t>Rosie DRANSFELD / 莊芳芳 ZHUANG Fan-fan</t>
         </is>
       </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>以「Rosie Dransfeld」＋「Last Catch」查詢，僅查得加拿大紀錄片導演 Rosvita（Rosie）Dransfeld 之其他作品（如《Broke》《Anti-Social Limited》《Her Last Project》），未查得片名為《Last Catch／漁人悲歌》之作品，亦未查得與莊芳芳（ZHUANG Fan-fan）共同掛名之紀錄片。無法確認此案是否完成。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1365,6 +1749,36 @@
           <t>吳汰紝 Wuna WU / 李孟津 Ging LEE</t>
         </is>
       </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.tfai.org.tw/en/filmmakers/2139</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>吳汰紝（Wuna WU）確為知名台灣紀錄片導演（代表作《雜菜記》《不是尋人啟事》等），但未查得片名為《帶孩子上班去 / Working, with Child Around》之作品紀錄，亦未查得與李孟津（Ging LEE）共同掛名之案子。可能為提案階段未完成或後續更名，建議另以台灣紀錄片資料庫（Taiwan Docs）逐筆核對吳汰紝完整作品列表。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1391,6 +1805,40 @@
           <t>吳皓 WU Hao / 入選阿姆斯特丹提案大會 Round Table 項目；獲得福特基金會補助；與 BBC、荷蘭 VPRO 電視台、丹麥電視台、CNEX 等合製；由 CAT&amp;Docs 發行；</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>成名之路 / The Road to Fame（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://movie.douban.com/subject/24753185/
+https://ccdf.cnex.org.tw/?p=5109
+https://en.wikipedia.org/wiki/Hao_Wu_(director)
+https://www.chinaindiefilm.org/films/%E6%88%90%E5%90%8D%E4%B9%8B%E8%B7%AF/?lang=zh-hans
+http://www.cnex.org.hk/cnex_all.php?id=290</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>吳皓（Hao Wu）執導，2013 年於 Sheffield Doc/Fest 首映，由 BBC Storyville、荷蘭 VPRO、丹麥 DR 與 CNEX 聯合製作，福特基金會等資助，2014 年洛杉磯亞美影展獲評審團大獎與最佳剪輯獎，proposer 欄位所載「與 BBC、VPRO、CNEX 等合製、由 CAT&amp;Docs 發行」皆與查證結果相符，可確認為同一計畫且已完成。CNEX 為共同出品方，惟其官方聯絡信箱頁面因本次網路存取限制無法逐字開啟核對，故信箱標記未查到，未貿然填寫。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1417,6 +1865,39 @@
           <t>曾茜 ZENG Xi / 周洋 ZHOU Yang</t>
         </is>
       </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>新片名／英文片名可能有異動：廢城記／废城记（提案名：廢城記，中文相同），英文正式名稱查得為《Wandering Village》（提案英文名：A Tale of Waste City）</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.chinaindiefilm.org/films/%E5%BA%9F%E5%9F%8E%E8%AE%B0/?lang=zh-hans
+https://video.friday.tw/movie/detail/18872
+https://visiblerecord.com/zh-hant/content/廢城記
+https://taiwancinema.bamid.gov.tw/Film/Filmcontent/?ContentUrl=88164</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>導演曾茜（1983 年生），2012–2015 年拍攝北京東小口垃圾回收基地河南籍移工的紀錄片《廢城記》，中文片名與提案相同；查得英文譯名為《Wandering Village》，與提案英文名《A Tale of Waste City》不同，惟中文核心內容（廢城／回收基地拆遷）高度吻合，判斷為同一計畫。查證結果中僅見曾茜掛名，未見提案共同提案人周洋（ZHOU Yang），無法確認周洋在最終完成版本中的角色。台灣電影網另列有《廢棄之城》片名，是否為同一片之台灣代理譯名待覆核。信箱因相關網站（chinaindiefilm.org、visiblerecord.com、台灣電影網）本次皆無法開啟逐字核對，故未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1443,6 +1924,37 @@
           <t>趙青 ZHOU Qing / （Original title: The Unforgettable）</t>
         </is>
       </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>我只認識你 / Please Remember Me（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/zh-tw/%E8%AF%B7%E4%BD%A0%E8%AE%B0%E4%BD%8F%E6%88%91
+https://siaoyin.com/InfoBig5/7975062696168410294</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>趙青執導，2017 年 11 月 17 日上映，78（大陸版 82）分鐘，記錄其舅公樹鋒與舅婆味芳晚年面對阿茲海默症的故事，編劇為製片人馮都與楊紫燁，中英片名皆與提案相同，可確認為同一計畫且已完成。信箱因相關網頁本次網路存取限制未能開啟逐字核對，故未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1469,6 +1981,38 @@
           <t>盧彥中 Adoing LU</t>
         </is>
       </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>南島盛艷之花 / The Dream in the Mirror（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=24vXFFRNuH0
+https://www.twreporter.org/a/photo-1oneimage-art-adiong-lu
+https://docs.tfi.org.tw/zh-hant/filmmakers/2376</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>盧彥中（Adiong／Adoing LU，1984 年生，嘉義人）2014 年作品，被攝者為柳依蘭，YouTube 上有標題明確為《南島盛艷之花 The Dream In the Mirror》的導演訪談片段，中英片名皆與提案相同，判斷已完成。導演其後於 2017 年另以「二瘋僧」名義成立寒山拾得有限公司，此為其後續公司名稱，非本片提案時期資訊。信箱未查到。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1495,6 +2039,36 @@
           <t>杜海 Vincent DU</t>
         </is>
       </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://movie.douban.com/celebrity/1357243/</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>杜海（Vincent DU）確有其人，為中國紀錄片導演／攝影師，曾任新聞攝影記者，於香港大學新聞及傳媒研究中心取得碩士學位，並獲英國政府 Chevening 獎學金赴倫敦 Goldsmiths 攻讀紀錄片碩士，其近作《留守者》（Those Who Stayed Behind）曾入選多個國際影展；但未查得片名為《搖滾日記 / Almost Famous》之作品，搜尋結果多為同名劇情片《成名在望》（Cameron Crowe, 2000）幹擾，無法確認此案是否完成。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1521,6 +2095,36 @@
           <t>解修遠 XIE Xiu-yuan</t>
         </is>
       </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>以「解修遠」＋「專護房」／「A State of the Old」查詢均無相符結果，未查得此導演或此片之任何公開紀錄，無法確認是否完成。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1545,6 +2149,40 @@
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>黃惠偵 HUANG Hui-zhen / （原提案片名：我的 T 媽媽 Original title: My T Mama）</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>新片名：我和我的T媽媽 / The Priestess Walks Alone（原提案片名：我的T媽媽 / My T Mama，proposer 欄位本身已註明此更名）</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/zh-tw/%E6%88%91%E5%92%8C%E6%88%91%E7%9A%84T%E5%AA%BD%E5%AA%BD
+https://buzzorange.com/citiorange/2017/04/21/the-priestess-walks-alone/
+https://www.youtube.com/watch?v=EbB8gPHuMJ8
+https://www.taiwangazette.org/news/2018/8/what-my-lesbian-mother-taught-me-an-interview-with-the-priestess-walks-alone-director-huang-hui-chen
+https://priestesswalksalone.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>黃惠偵執導，記錄其母親身為牽亡陣藝師、同志身分與家庭創傷的故事，2016 年獲第 38 屆金穗獎首獎、南方影展評審團獎及人權關懷獎；2016 女性影展、金穗獎影展皆以《我和我的T媽媽 The Priestess Walks Alone》為片名放映，與資料列 zh／en 欄位內容（雖欄位被拆錯）完全吻合，proposer 欄位亦自行註明原提案片名為《我的T媽媽 My T Mama》，可確認片名確實更動且影片已完成、並有多次影展放映紀錄。信箱因原片官方部落格（priestesswalksalone.wordpress.com）等頁面本次網路存取限制未能開啟逐字核對，故未查到。</t>
         </is>
       </c>
     </row>
@@ -3780,6 +4418,40 @@
           <t>陳思毅 CHEN Siyi</t>
         </is>
       </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>我们在黑夜的海上 / Dear Mother, I Meant to Write about Death（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.idfa.nl/en/film/0282cd59-5d22-454b-8077-8133acab8058/dear-mother-i-meant-to-write-about-death/
+https://www.imdb.com/title/tt22049324/
+https://www.cinemaescapist.com/2023/07/review-dear-mother-write-about-death-movie/
+https://www.siyichenfilm.com/
+https://hk.cnexdoc.com/zh/news/2222/</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>導演陳思毅（Siyi Chen）以此片作為劇情長片首作，2022 年釜山影展世界首映（獲亞洲紀錄片競賽評審團特別提及），並入選 IDFA 2022 最佳首作競賽。片名與提案名一致。導演個人網站 siyichenfilm.com 因環境網路存取限制（WebFetch 被擋）無法讀取聯絡頁面，故無法核實公開 email。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3806,6 +4478,40 @@
           <t>杜海 Vincent DU</t>
         </is>
       </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>新片名：江南棄兒 / China's Forgotten Daughters（提案名：江南女兒）</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt7227928/
+http://vincentdu.com/chinas-forgotten-daughters/
+https://www.chinaindiefilm.org/films/chinas-forgotten-daughters/
+https://asianmoviepulse.com/2020/07/documentary-review-chinas-forgotten-daughters-2018-by-meng-han-and-vincent-du/
+https://multimedia.lib.thu.edu.tw/?p=41328</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>2018 年完成，由杜海（Vincent Du）與韓萌（Han Meng）共同執導，正式中文片名為《江南棄兒》而非提案的《江南女兒》，英文名與提案一致。導演個人網站 vincentdu.com 因環境網路存取限制無法讀取，未能核實公開 email。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3832,6 +4538,38 @@
           <t>霍寧 HOU Ning / 史祖德 Gary SHIH</t>
         </is>
       </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>拉一碗麵 / Noodle Kid（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt11672118/
+https://festival.vcmedia.org/2020/movies/noodle-kid/
+https://www.youtube.com/watch?v=wWpcD9iuENk</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>2019 年完成，於釜山影展 Wide Angle 單元獲最佳紀錄片，並入選 2020 洛杉磯亞太影展。片名與提案相同。因 WebFetch 在此環境被整體阻擋，無法進一步查證公開聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3858,6 +4596,37 @@
           <t>旦增色珍 Tenzinsedon / 廖茗 Ming</t>
         </is>
       </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>孜廓路 / Tsekhor（提案名相同，未能確認正式定名或是否即為同一部完成作品）</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>https://v.qq.com/x/page/t01757czch5.html
+https://ccdf.cnexdoc.com/en/ccdf-years/ccdf-07/</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>搜尋到騰訊視頻上有一部同名《孜廓路》影片，但因搜尋結果片段未載明導演姓名，無法確認是否為旦增色珍（Tenzinsedon）與廖茗提案的同一部作品；且因本輪 WebSearch 額度已用盡、WebFetch 又被環境整體阻擋，無法點開該連結逐一核實內容與導演資訊，故完成度與正式片名均判定為未查到，僅供後續人工複查參考。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3884,6 +4653,39 @@
           <t>李哲昕 Jill LI</t>
         </is>
       </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>迷航 / Lost Course（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tfai.org.tw/program/movieDetail/2c9580827f62c38d017f8718ff6c0041
+https://letterboxd.com/film/lost-course/
+https://www.twreporter.org/a/2020-taipei-golden-horse-film-festival-lost-course
+https://mulanfestival.com/lost-course/</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>香港導演李哲昕（Jill Li）作品，2019/2020 年完成，獲 2020 金馬獎最佳紀錄片、2021 TIDF 亞洲視野競賽優等獎等，並入選 IDFA、溫哥華影展等。片名中英文均與提案相同。導演相關公司網頁（Eye Catcher / Visual Suspect）因 WebFetch 被環境阻擋無法讀取，未能核實公開 email。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3910,6 +4712,36 @@
           <t>王楊 WANG Yang / 王國慶 WANG Guo-qing</t>
         </is>
       </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>江橋夢 / The Dream of Super Bridge（與提案名相同，惟僅查到提案／入選其他提案大會的紀錄，未查到後續完成或發行資訊）</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>https://hk.cnexdoc.com/zh/themed-screening/1450/</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>僅查到王楊（WANG Yang）此案於 2016 年廣州國際紀錄片節提案大會入選十強、2017 年東山國際紀錄片提案大會獲銀獎等「提案階段」紀錄，並無後續完成、影展放映或發行的訊息，故完成度判定為未查到。王楊本人另有其他已知作品（如《地上空間》《中國門》），但與本片非同一部。本輪 WebSearch 額度已用盡，未能進一步查證。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3936,6 +4768,36 @@
           <t>陳文良 Martin CHEN</t>
         </is>
       </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：逆者 / The Road Less Traveled，提案人陳文良 Martin CHEN）</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>本項目研究時，環境的 WebSearch 額度已用盡（該額度似為整個 session 所有平行作業共用），且 WebFetch 工具在本環境被整體阻擋（包含 Google、IMDb、Wikipedia 等常見查證來源），因此完全未能進行查證，所有欄位皆為未查到，需另行人工或以其他工具複查。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3962,6 +4824,36 @@
           <t>陳東楠 Dongnan CHEN</t>
         </is>
       </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：曠野歌聲 / Singing in the Wilderness，提案人陳東楠 Dongnan CHEN）</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>同上，因 WebSearch 額度已用盡、WebFetch 被環境整體阻擋，本項目完全未能查證，需另行複查。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3988,6 +4880,36 @@
           <t>侯婕 Jess HAO 陳庭婷 Kiwi CHAN / （原提案片名： 超齡爸媽 Original title: The Parents Dream）                                        周浩 ZHOU Hao</t>
         </is>
       </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：議事亭前地的媽媽 / Mama Dream Of Family；proposer 欄位混亂，疑似含另一提案「超齡爸媽 / The Parents Dream」之原片名註記，提案人可能為侯婕 Jess HAO、陳庭婷 Kiwi CHAN，另欄位中出現周浩 ZHOU Hao 疑為欄位錯置或掛名顧問）</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>proposer 欄位資料明顯錯亂（同時出現兩組人名與一組「原提案片名」註記），且因 WebSearch 額度已用盡、WebFetch 被環境整體阻擋，完全未能查證，需另行人工複查以釐清正確提案人與片名。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4012,6 +4934,36 @@
       <c r="F89" s="2" t="inlineStr">
         <is>
           <t>滕仲愷 TENG Zhong kai / 張獻民 ZHANG Xianmin</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：水下 / Underwater，提案人滕仲愷 TENG Zhong kai / 張獻民 ZHANG Xianmin）</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>同上，因 WebSearch 額度已用盡、WebFetch 被環境整體阻擋，本項目完全未能查證，需另行複查。</t>
         </is>
       </c>
     </row>

--- a/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
+++ b/outreach-research/CCDF_歷屆提案_完成狀態與聯絡資訊.xlsx
@@ -3564,6 +3564,36 @@
           <t>紀岳君 CHI Yueh-chun / （原提案片名：女王魔咒 Original title: The Devil in Confession）                   蕭立峻 Richard HSIAO</t>
         </is>
       </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：徐自強的練習題 / Condemned Practice Mode，提案人紀岳君、蕭立峻，原提案片名：女王魔咒）因工具限制未能查證：查證途中 WebSearch 已達本工作階段查詢上限（200／200），且 WebFetch 對所有外部網域皆回傳 network egress proxy 封鎖（含 example.com 測試亦失敗），故完全無法進行後續查證，未查到任何資訊。建議日後在有可用之 WebSearch／WebFetch 額度時重新查證。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3590,6 +3620,36 @@
           <t>溫澤仁 Hau Man WAN / （原提案片名：酷兒 Original title: All About Myself）</t>
         </is>
       </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：假若我有靈魂 / Kaspar X – If I Had a Soul，提案人溫澤仁，原提案片名：酷兒／All About Myself）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3616,6 +3676,36 @@
           <t>Lola LIU</t>
         </is>
       </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：奈何橋 / On the Bridge of Death and Life，提案人 Lola LIU）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3642,6 +3732,36 @@
           <t>廖憶玲 LIAO I-ling / （Original title: LI Yuan-chia: Tell Me What Is Not Yet Said）           朱柏穎 CHU Po-ying</t>
         </is>
       </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：尋找．另一個故事 / All and Nothing，原提案片名：LI Yuan-chia: Tell Me What Is Not Yet Said，提案人廖憶玲、朱柏穎）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3668,6 +3788,36 @@
           <t>蘇青 SU Qing 米娜 Mina</t>
         </is>
       </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：梧桐樹 / Caro Mio Ben (My Dear Beloved)，提案人蘇青、米娜）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3694,6 +3844,36 @@
           <t>潘志琪 PAN Zhi-qi / 入圍 ASD 亞洲陽光紀錄片大會「中國提案日」、入選 2015 年浙江省文化精品扶持工程、入選 2016 印度 Docedge 紀錄片論壇；2015 the Asian</t>
         </is>
       </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：二十四號大街／24th Street，提案人潘志琪，曾入圍 ASD 亞洲陽光紀錄片大會中國提案日、2015 浙江省文化精品扶持工程、2016 印度 Docedge 論壇）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3718,6 +3898,36 @@
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>胡斯翰 Stephen Gurie WOO / （原提案片名：廿雙巧手）                                                           宋軒麟 Alfred SUNG</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>本專案（提案名：雙縫 / The Tailors，原提案片名：廿雙巧手，提案人胡斯翰、宋軒麟）因工具限制未能查證：WebSearch 已達本工作階段查詢上限（200／200），WebFetch 對所有外部網域皆被 network egress proxy 封鎖，無法進行任何查證。</t>
         </is>
       </c>
     </row>
@@ -5621,6 +5831,40 @@
           <t>韓萌 HAN Meng</t>
         </is>
       </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>遙望繁星 / Smog Town（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt12286368/
+http://www.catndocs.com/index.php/categories/health/1076-smog-town
+https://dafilms.com/film/11114-smog-town
+https://www.docnyc.net/film/smog-town/
+https://www.idfa.nl/en/film/ad33842f-b633-4cab-afeb-194284e17fc4/smog-town/docs-for-sale/</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>已於 2019 年完成，2020 年於 IDFA／Visions du Réel 等多個國際影展放映，國際銷售由法國 CAT&amp;Docs 代理。導演韓萌與 CCDF 提案時同名，片名未變。搜尋範圍內找不到導演或 CAT&amp;Docs 的公開 email（CAT&amp;Docs 官網 catndocs.com 被本環境的 egress proxy 擋下，無法直接讀取聯絡頁）。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5647,6 +5891,40 @@
           <t>盧盈良 Elvis LU / （原提案片名：阿志 Original title: My Psychic Brother）                              李建良 LI Jian-liang</t>
         </is>
       </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>神人之家 / A Holy Family（與提案名相同；提案階段曾用暫定片名《阿志 / My Psychic Brother》）</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.goldenhorse.org.tw/film/about/archive/detail/3437
+https://zh.wikipedia.org/zh-tw/%E7%A5%9E%E4%BA%BA%E4%B9%8B%E5%AE%B6
+https://www.twreporter.org/a/2022-taipei-golden-horse-film-festival-holy-family
+https://www.tidf.org.tw/zh-hant/films/134201
+https://funscreen.tfai.org.tw/article/38262</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>2022 年完成上映，入圍第 59 屆金馬獎最佳紀錄片、最佳剪輯，並拿下第 24 屆台北電影獎百萬首獎等 4 項大獎。導演盧盈良（Elvis Lu），出品公司為飛望影像有限公司（負責人陳璽文）。查到公司電話（02-25210710）與地址，但公開資料中未找到 email；官方頁面（金馬、TIDF）皆被 egress proxy 擋下無法直接讀取聯絡資訊。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5673,6 +5951,37 @@
           <t>陳英尉 CHAN Ying-wai / 李敏芝 LI Man-chi</t>
         </is>
       </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>工筆放肆 / In Between Worlds（提案名，未確認是否有正式定案片名）</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/inbetweenworlds.thefilm
+https://www.haf.org.hk/wiplabproject.php?cid=4</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>搜尋結果混雜多個同名或近似名稱的不同作品（香港畫家石家豪 Wilson Shieh 的紀錄片計畫、美國 Winnemem Wintu 部落紀錄片《In Between Worlds》等），皆與提案人陳英尉／李敏芝對不上，無法確認此案是否即為 2020 年入選香港 HAF（Hong Kong Asia Film Financing Forum）之計畫，也未查到完成或上映紀錄。Facebook 專頁 inbetweenworlds.thefilm 與 HAF 官網皆因本環境 egress proxy 限制無法讀取內容，導致無法進一步比對。建議之後有網路存取權限時針對「陳英尉 李敏芝 紀錄片」與 HAF 2020 片單重新查證。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5699,6 +6008,39 @@
           <t>羅苡珊 LO Yi-shan</t>
         </is>
       </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>雪水消融的季節 / After the Snowmelt（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.tfai.org.tw/zh-hant/film/7028
+https://www.goldenhorse.org.tw/film/about/archive/detail/4023
+https://taicca.tw/intelligence/story_scene/detail/14
+http://www.iwant-radio.com/showinformation.php?sisn=56223</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>導演羅苡珊歷時 7 年完成的首部紀錄長片，2024 年完成，入選瑞士真實影展、韓國全州影展、美國 Frameline 等，並獲台北電影節媒體推薦獎。共同製作為希望影視行銷股份有限公司與紀錄片夢想中心。查到希望影視行銷之電話（+886 2 8941-0166）及地址，未查到公開 email。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5725,6 +6067,38 @@
           <t>許慧晶 XU Hui-jing</t>
         </is>
       </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>棒！少年 / Tough Out（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iqiyi.com/lib/m_3213175573804414.html
+https://movie.douban.com/subject/34930862/
+https://www.youtube.com/watch?v=W3xCXYqz3Cg</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>2020 年 12 月 11 日中國大陸院線上映，並獲第 14 屆 FIRST 青年電影展最佳紀錄片。導演許慧晶。搜尋中未能確認正式出品公司全名及其公開 email；豆瓣工作人員頁面因 egress proxy 限制無法直接讀取以核對出品／發行公司聯絡方式。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5751,6 +6125,36 @@
           <t>莎韻西孟 Sayun Simung</t>
         </is>
       </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>烤火房的一些夢 / Lost in Dreams（提案名，未確認是否為最終片名）</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>本次研究過程中，WebSearch 工具額度已於前 5 案（row 102–106）用盡（達到本 session 200 次上限），且 WebFetch 對絕大多數目標網域（Wikipedia、豆瓣、IMDb、TIDF、金馬、台灣電影網、TaiwanDocs、Facebook、CNEX/CCDF 官網等）皆被本環境 egress proxy 擋下，導致完全無法對此案（導演莎韻西孟 Sayun Simung）進行任何查證。建議日後在有完整網路存取權限時重新研究。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5777,6 +6181,36 @@
           <t>提姆柯爾 Tim COLE / 陳玟臻 BaoBao CHEN</t>
         </is>
       </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>小島大歌 / Small Island Big Song（提案名，未確認是否為最終片名）</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>同 row 107，因 WebSearch 額度已用盡、WebFetch 又被 egress proxy 大量擋下，無法對導演提姆柯爾（Tim Cole）／陳玟臻（BaoBao Chen）之作品進行查證。依既有背景知識此片為 2018 年前後已完成並於多國影展放映之太平洋南島音樂紀錄片，但因本次未能實際查證公開來源，依規則標記為未查到，不採信未經查證的記憶。建議重新查證官網 islandsong.org、CNEX/CCDF 及各大影展資料。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5829,6 +6263,36 @@
           <t>張琳 ZHANG Lin / 粟國祥 SU Guo-xiang</t>
         </is>
       </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>真實生長 / Dare to Grow Up（提案名，未確認是否為最終片名）</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>因 WebSearch 額度已用盡、WebFetch 被 egress proxy 大量擋下，無法對導演張琳／粟國祥之作品進行查證，依規則不採信未經查證之背景記憶，標記為未查到。建議重新查證豆瓣、CNEX 官網及中國大陸串流平台。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5881,6 +6345,36 @@
           <t>劉春雨 LIU Chun-yu / 任曉宇 REN Xiao-yu</t>
         </is>
       </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>翁丁 / The Last Tribe in China（提案名，未確認是否為最終片名）</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>因 WebSearch 額度已用盡、WebFetch 被 egress proxy 大量擋下，無法對導演劉春雨／任曉宇之作品進行查證，標記為未查到。備註：雲南滄源翁丁佤族古寨於 2021 年 2 月發生大火焚毀，若此片與該事件相關，後續查證時可作為線索。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5905,6 +6399,36 @@
       <c r="F113" s="2" t="inlineStr">
         <is>
           <t>周浩 ZHOU Hao 賀珊 HE Shan / 2019 年參加西湖紀錄片大會，獲得最佳入門獎第二名；入選 2021 上海電影節、FIRST 青年電影展</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>孤注 / All In（提案名，未確認是否為最終片名）</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>資料本身備註提及「2019 年參加西湖紀錄片大會，獲得最佳入門獎第二名；入選 2021 上海電影節、FIRST 青年電影展」，顯示此案很可能已完成並曾入選影展，但因 WebSearch 額度已用盡、WebFetch 被 egress proxy 大量擋下，本次無法實際查證官方確認來源或找到公開 email，故完成狀態保守標記為未查到，不依未查證資訊直接判定「是」。建議重新查證豆瓣、FIRST 青年電影展及上海電影節官方片單。</t>
         </is>
       </c>
     </row>
@@ -6019,6 +6543,36 @@
           <t>蘇美玉 SU Mei-yu 洪伯豪 HUNG Po-hao</t>
         </is>
       </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6045,6 +6599,36 @@
           <t>楊圓圓 Luka Yuanyuan YANG / 丁大衛 DING Da-wei 鄒艾暘 ZOU Ai-yang</t>
         </is>
       </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6066,6 +6650,36 @@
           <t>康宇琪 KANG Yu-qi 曹曦 CAO Xi / （Original title: Inspirare）                                            Dana Kalmey</t>
         </is>
       </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6092,6 +6706,36 @@
           <t>劉湘晨 LIU Xiang-chen 徐秋麗 XU Qiu-li / 2020 廣州國際紀錄片節提案大會 (GZDOC)</t>
         </is>
       </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6118,6 +6762,36 @@
           <t>賴冠源 LAI Kuan-Yuan</t>
         </is>
       </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6144,6 +6818,36 @@
           <t>范立欣 FAN Li-xin</t>
         </is>
       </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6170,6 +6874,36 @@
           <t>尚若白 Jean-Robert THOMANN / （原提案片名：苦伶的臉譜）                                                                  黃郁茜 Garance HUANG</t>
         </is>
       </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6190,6 +6924,36 @@
           <t>譚墨 TAN Mo / The Confession of a Mole                                                       李姍姍 LI Shan-shan</t>
         </is>
       </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6242,6 +7006,36 @@
           <t>陳潔瑤 Laha Mebow</t>
         </is>
       </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>未查詢：本 session 的 WebSearch 額度（200 次）已用盡，且網路政策擋下多數網站，此筆完全沒有搜尋，需要重新查詢。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6268,6 +7062,38 @@
           <t>賀照緹 HO Chao-ti</t>
         </is>
       </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>睏寐之際 / The Sleep Goddess（提案英文名：Hypnos，正式上映後英文片名改為 The Sleep Goddess）</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rti.org.tw/radio/programMessageView/id/151360
+https://www.facebook.com/TheSleepGoddess.film/
+https://tw.news.yahoo.com/%E8%B3%80%E7%85%A7%E7%B7%B9%E7%AA%81%E7%A0%B4%E8%88%92%E9%81%A9%E5%9C%88-%E7%B4%80%E9%8C%84%E7%89%87-%E7%9D%8F%E5%AF%90%E4%B9%8B%E9%9A%9B-%E7%8D%BB%E7%B5%A6%E5%A4%B1%E7%9C%A0%E5%9C%8B%E5%BA%A6%E6%89%93%E6%8B%9A%E7%9A%84%E4%BA%BA-045600895.html</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>由賀照緹執導，以民俗神明「床母」為主觀視角，2024 年 6 月 7 日全台正式上映，片長 79 分鐘，屬已完成並發行的作品。提案英文名為 Hypnos（希臘睡神），上映時英文片名確認為 The Sleep Goddess，中文片名維持不變。製作公司為大照國際影像有限公司，發行為牽猴子股份有限公司；未能在公開頁面找到導演或製作公司的聯絡 email（僅有 Facebook 粉專，無法存取確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6294,6 +7120,36 @@
           <t>邱繼亮 CHIU Chi-liang / 黎靜如 LI Jing-ru</t>
         </is>
       </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>未查到（提案名：公斤 25 / kg）</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>以「公斤 25」「kg」搭配導演邱繼亮、黎靜如進行多次搜尋，均未找到對應的完成作品、影展紀錄或報導；也未在 CCDF 官網（ccdf.cnexdoc.com，本次連線被網路代理阻擋無法存取）以外找到資料。無法確認此片是否完成，亦無法確認正式片名或聯絡方式。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6320,6 +7176,36 @@
           <t>陳德明 CHEN De-ming / 郭謀銑 GUO Mou-xiang</t>
         </is>
       </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>從來 / Always（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>https://funscreen.tfai.org.tw/article/38885</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>導演陳德明，於 2025 年 3 月在 CPH:DOX 哥本哈根國際紀錄片影展世界首映並奪得主競賽單元最大獎，5 月於韓國全州影展國際競賽單元獲 Best Picture Prize（第二大獎），確認已完成。惟查得之製片為林漢森，與原始資料 proposer 欄位所載「郭謀銑」不同，無法確認郭謀銑與本片之關係（可能為原始資料誤植或為另一位工作人員），請留意核對。因 funscreen.tfai.org.tw 頁面被網路代理阻擋，無法進一步讀取全文以尋找聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6346,6 +7232,37 @@
           <t>梁丑娃 LIANG Chou-wa</t>
         </is>
       </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>Replica（英文與提案名相同；中文提案名「複製戀人」，中文正式譯名未見統一使用，兩篇報導分別譯為「複製戀人」與「複製品」）</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>https://pancouver.ca/%E5%9C%A8%E7%B4%80%E9%8C%84%E7%89%87%E3%80%8Areplica%E3%80%8B%E4%B8%AD%EF%BC%8C%E6%A2%81%E9%86%9C%E5%A8%83%E6%8E%A2%E7%B4%A2%E4%B8%AD%E5%9C%8B%E5%A5%B3%E6%80%A7%E8%88%87%E4%BA%BA%E5%B7%A5%E6%99%BA/
+https://variety.com/2026/film/global/replica-chouwa-liang-thessaloniki-1236680817/</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>導演梁丑娃（Chouwa LIANG，另見譯名梁醜娃），紀錄三位中國女性與 AI 男友的親密關係，已於 Thessaloniki Documentary Festival（塞薩洛尼基紀錄片影展）世界首映，並獲 Variety 專訪報導，確認已完成。原始資料 proposer 欄位僅列梁丑娃一人，與查得資訊相符。pancouver.ca 與 variety.com 頁面皆被網路代理阻擋，無法進一步讀取全文尋找聯絡 email 或銷售代理資訊。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6372,6 +7289,39 @@
           <t>許明淳 HSU Ming-chun / 李嘉雯 Diana Chiawen LEE</t>
         </is>
       </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>冰封的記憶 / Memories Frozen in Time（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>https://www.taipeitimes.com/News/taiwan/archives/2026/09/10/2003864012
+https://focustaiwan.tw/culture/202609090015
+https://www.hwe-hon.com.tw/product_detail.php?pid=3492
+https://www.unfiltered.coop/memories-frozen-in-time/</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>導演許明淳，紀錄二戰後遭蘇聯拘留於西伯利亞的台籍戰俘，片長 86 分鐘，已於公視「紀錄觀點」及 PTV+ 平台播映，2026 年 9 月見於 Taipei Times、Focus Taiwan 等英文媒體報導，確認已完成並發行。中英片名與提案名一致。因多個相關頁面（taipeitimes.com、hwe-hon.com.tw、unfiltered.coop、flyingv.cc）皆被網路代理阻擋，無法進一步讀取全文尋找聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6393,6 +7343,36 @@
           <t>吳哲維 Chris WU / 徐沛希 Beverly HSU</t>
         </is>
       </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>新片名：伴忘日記1825 Days（提案名：Days，中文提案原缺）</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>https://ccdf.cnexdoc.com/zh-tw/ccdf-awarded/5247/</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>導演吳哲維、製片徐沛希，CCDF-14 得獎項目正式登記名稱為「伴忘日記1825 Days」（提案時中文欄位原為空，英文為 Days），內容為長達近六年的母女長照陪伴紀實。僅查得 CCDF 官方提案頁面（ccdf.cnexdoc.com 本次被網路代理阻擋無法讀取全文）與 Podcast 訪談，未查到正式上映、影展放映或廣播紀錄，無法確認是否已完成製作；亦未查到聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6419,6 +7399,37 @@
           <t>王安民 WANG An-min / 周玠萱 CHOU Chieh-hsuan</t>
         </is>
       </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>高山遊民 / The Rover（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vscinemas.com.tw/film/detail.aspx?id=8468
+https://www.peopo.org/news/831999</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>導演王安民，歷時 4 年、50 趟登山蹲點拍攝百岳挑夫「阿共」的生命故事，已於威秀影城上映並在嘉義返鄉舉辦首映講座，確認已完成並發行。英文片名 The Rover 見於官方 Facebook 粉專名稱，與提案名相符。查得之攝影師為陳俊逸，與原始資料 proposer 欄位所載「周玠萱」不同，無法確認周玠萱與本片之關係（可能為製片或原始資料誤植），請留意核對。未查到聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -6445,6 +7456,40 @@
           <t>陳東楠 CHEN Dong-nan</t>
         </is>
       </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>清花的五月 / Whispers in May（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>https://variety.com/2026/film/reviews/whispers-in-may-review-1236688538/
+https://variety.com/2026/film/global/whispers-in-may-dongnan-chen-cph-dox-1236688422/
+https://www.hollywoodreporter.com/movies/movie-news/whispers-in-may-doc-film-interview-cphdox-china-womanhood-1236528981/
+https://uniondocs.org/event/whispers-in-may-2026-05-02/
+https://www.visionsdureel.ch/en/film/2026/whispers-in-may/</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>導演陳東楠（Dongnan CHEN），紀錄四川涼山彝族少女成年禮的半紀實半劇情作品，2026 年 3 月 15 日於 CPH:DOX 哥本哈根國際紀錄片影展主競賽單元世界首映並獲頒 DOX:AWARD，其後於 Visions du Réel、UnionDocs、Hot Docs 等場合放映，確認已完成並廣泛發行。中英片名與提案名一致。因 variety.com、hollywoodreporter.com 等頁面被網路代理阻擋，無法進一步讀取全文尋找聯絡 email 或銷售代理資訊。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -6471,6 +7516,38 @@
           <t>施儀潔 Claire SHIH</t>
         </is>
       </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>揹笭的粉鳥 / Do Pigeons Want to Go Home?（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>https://viewpoint.pts.org.tw/zh_tw/video/pts/%E6%8F%B9%E7%AC%AD%E7%9A%84%E7%B2%89%E9%B3%A5Do-Pigeons-Want-to-Go-Hme-24024580
+https://stars.udn.com/star/story/10090/8799601
+https://ccdf.cnexdoc.com/en/news/4585/</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>導演施儀潔（Claire SHIH），紀錄台南北邊農村魏氏父子三代熱衷「粉鳥笭」（賽鴿遊戲）的故事，經一年半蹲點拍攝，已於 2025 年 6 月 12 日在公視「紀錄觀點」首播並於公視 YouTube 同步播出，確認已完成並播映。查得共同導演／攝影為 Ray CHAN（陳淦熙），並曾獲 CCDF-14 本土題材特別獎；原始資料 proposer 欄位僅列施儀潔一人，未提及共同創作者，可能為原始資料簡化所致。片名與提案名相符（公視頁面網址中片名誤植為「Go Hme」，屬網址拼字錯誤，正式片名仍為「Go Home?」）。未查到聯絡 email。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6495,6 +7572,37 @@
       <c r="F135" s="2" t="inlineStr">
         <is>
           <t>范儉 Jian FAN / 杜海 Vincent DU</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>无端欢喜 / I Still Want（與提案名相同）</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>https://ccdf.cnexdoc.com/zh-cn/ccdf-awarded/5140/
+https://zh.wikipedia.org/zh-tw/%E8%8C%83%E4%BF%AD</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>導演范儉（Jian FAN）、製片杜海（Vincent DU）。范儉為中國知名紀錄片導演，代表作《搖搖晃晃的人間》。本片涉及詩人余秀華，僅查得 CCDF 官方提案登記頁面（ccdf.cnexdoc.com 本次被網路代理阻擋無法讀取全文），未查到正式完成、首映或影展放映的公開紀錄，無法確認是否已完成製作；亦未查到聯絡 email。</t>
         </is>
       </c>
     </row>
